--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_322_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_322_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>7</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>10</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2707,16 +2707,16 @@
         <v>33</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X24" t="n">
         <v>12</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>122</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>38</v>
@@ -4488,10 +4488,10 @@
         <v>24</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>18</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X38" t="n">
         <v>4</v>
@@ -5272,7 +5272,7 @@
         <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>26</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>130</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>33</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_322_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_322_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>9</v>
@@ -851,20 +851,20 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>86.84</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>4</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>3</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
@@ -4936,14 +4936,14 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5284,10 +5284,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Y48" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
